--- a/data/codebook.xlsx
+++ b/data/codebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drexel0-my.sharepoint.com/personal/lf649_drexel_edu/Documents/Research/South Philly R21/Papers/Analysis Paper/thriveair_analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="8_{A43FBEE1-7DC7-3B42-A486-5D77B8D1FA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{189563F2-5EEC-48F5-A763-C5E209EB50A0}"/>
+  <xr:revisionPtr revIDLastSave="420" documentId="8_{A43FBEE1-7DC7-3B42-A486-5D77B8D1FA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B7ADB0F-3D95-48CB-9F46-FC4F6539A53F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7B683D2B-6783-FD48-99CD-8A550E8E5759}"/>
+    <workbookView xWindow="-23430" yWindow="-45" windowWidth="21945" windowHeight="12315" xr2:uid="{7B683D2B-6783-FD48-99CD-8A550E8E5759}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="98">
   <si>
     <t>btex</t>
   </si>
@@ -59,24 +59,12 @@
     <t>Ethylbenzene</t>
   </si>
   <si>
-    <t>Xylenes</t>
-  </si>
-  <si>
     <t>Total BTEX</t>
   </si>
   <si>
     <t>1,2-dichlorobenzene</t>
   </si>
   <si>
-    <t>1-ethyl-2-methyl-benzene</t>
-  </si>
-  <si>
-    <t>1-ethyl-3-methyl-benzene</t>
-  </si>
-  <si>
-    <t>1-ethyl-4-methyl-benzene</t>
-  </si>
-  <si>
     <t>Decane</t>
   </si>
   <si>
@@ -86,12 +74,6 @@
     <t>Heptane</t>
   </si>
   <si>
-    <t>3-methyl-heptane</t>
-  </si>
-  <si>
-    <t>2-methyl-hexane</t>
-  </si>
-  <si>
     <t>Mesitylene</t>
   </si>
   <si>
@@ -104,9 +86,6 @@
     <t>Tetrachloroethylene</t>
   </si>
   <si>
-    <t>Trichloromonofluoromethane</t>
-  </si>
-  <si>
     <t>Undecane</t>
   </si>
   <si>
@@ -203,9 +182,6 @@
     <t>Alkanes</t>
   </si>
   <si>
-    <t>Branched Alkanes</t>
-  </si>
-  <si>
     <t>Alkylbenzenes</t>
   </si>
   <si>
@@ -327,6 +303,33 @@
   </si>
   <si>
     <t>(m+p)-Xylenes</t>
+  </si>
+  <si>
+    <t>2-Methylhexane</t>
+  </si>
+  <si>
+    <t>3-Methylheptane</t>
+  </si>
+  <si>
+    <t>1-Ethyl-2-Methylbenzene</t>
+  </si>
+  <si>
+    <t>1-Ethyl-3-Methylbenzene</t>
+  </si>
+  <si>
+    <t>1-Ethyl-4-Methylbenzene</t>
+  </si>
+  <si>
+    <t>Trichlorofluoromethane</t>
+  </si>
+  <si>
+    <t>Other Alkanes</t>
+  </si>
+  <si>
+    <t>sort_in_category</t>
+  </si>
+  <si>
+    <t>Total Xylenes</t>
   </si>
 </sst>
 </file>
@@ -678,15 +681,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B9F5C7-AD20-C34E-A562-0D3609500FD0}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="19.375" customWidth="1"/>
-    <col min="5" max="5" width="32.375" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -697,235 +700,271 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="G1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C2">
-        <v>78.11</v>
+        <v>106.16</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>92.14</v>
+        <v>78.11</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>106.17</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>106.16</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>92.14</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7">
-        <v>106.16</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>106.16</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C9">
-        <v>120.19</v>
+        <v>120.194</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C10">
-        <v>120.19</v>
+        <v>134.221</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C11">
         <v>120.19</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>120.19</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="B13" t="s">
         <v>37</v>
@@ -934,307 +973,352 @@
         <v>120.19</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="C14">
-        <v>120.194</v>
+        <v>120.19</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="C15">
-        <v>134.221</v>
+        <v>120.19</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C16">
-        <v>114.23</v>
+        <v>100.21</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C17">
-        <v>100.2</v>
+        <v>86.18</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="C18">
-        <v>72.150999999999996</v>
+        <v>128.25</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C19">
-        <v>86.177999999999997</v>
+        <v>114.23</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="C20">
+        <v>149.29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>170.34</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22">
+        <v>156.31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23">
+        <v>114.232</v>
+      </c>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24">
+        <v>100.205</v>
+      </c>
+      <c r="D24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25">
+        <v>100.2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26">
+        <v>114.23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27">
+        <v>100.205</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28">
         <v>86.177999999999997</v>
       </c>
-      <c r="D20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21">
-        <v>100.205</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22">
-        <v>114.232</v>
-      </c>
-      <c r="D22" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" t="s">
-        <v>55</v>
-      </c>
-      <c r="F22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>84</v>
-      </c>
-      <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23">
-        <v>100.205</v>
-      </c>
-      <c r="D23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24">
-        <v>100.21</v>
-      </c>
-      <c r="D24" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25">
-        <v>86.18</v>
-      </c>
-      <c r="D25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26">
-        <v>128.25</v>
-      </c>
-      <c r="D26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27">
-        <v>114.23</v>
-      </c>
-      <c r="D27" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28">
-        <v>149.29</v>
-      </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
         <v>95</v>
@@ -1242,19 +1326,22 @@
       <c r="F28">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C29">
-        <v>170.34</v>
+        <v>86.177999999999997</v>
       </c>
       <c r="D29" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
         <v>95</v>
@@ -1262,19 +1349,22 @@
       <c r="F29">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C30">
-        <v>156.31</v>
+        <v>72.150999999999996</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
         <v>95</v>
@@ -1282,230 +1372,267 @@
       <c r="F30">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C31">
         <v>98.188999999999993</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32">
+        <v>84.162000000000006</v>
+      </c>
+      <c r="D32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32">
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33">
         <v>70.132900000000006</v>
       </c>
-      <c r="D32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32">
+      <c r="D33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33">
+        <v>6</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34">
+        <v>68.12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35">
+        <v>100.161</v>
+      </c>
+      <c r="D35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33">
-        <v>68.12</v>
-      </c>
-      <c r="D33" t="s">
-        <v>74</v>
-      </c>
-      <c r="E33" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33">
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36">
+        <v>100.16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" t="s">
+        <v>68</v>
+      </c>
+      <c r="F36">
         <v>7</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34">
-        <v>84.162000000000006</v>
-      </c>
-      <c r="D34" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F34">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35">
-        <v>100.16</v>
-      </c>
-      <c r="D35" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" t="s">
-        <v>76</v>
-      </c>
-      <c r="F35">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36">
-        <v>100.161</v>
-      </c>
-      <c r="D36" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" t="s">
-        <v>76</v>
-      </c>
-      <c r="F36">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C37">
         <v>147.01</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E37" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F37">
         <v>8</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C38">
-        <v>165.83</v>
+        <v>153.81</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F38">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39">
-        <v>137.37</v>
+        <v>119.37</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E39" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F39">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C40">
-        <v>119.37</v>
+        <v>165.83</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F40">
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C41">
-        <v>153.81</v>
+        <v>137.37</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E41" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F41">
         <v>8</v>
       </c>
+      <c r="G41">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F41">
-    <sortCondition ref="F1:F41"/>
+    <sortCondition ref="F2:F41"/>
+    <sortCondition ref="A2:A41"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
